--- a/data/valuebets_database_2025-07-13.xlsx
+++ b/data/valuebets_database_2025-07-13.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I22"/>
+  <dimension ref="A1:I25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -505,10 +505,8 @@
           <t>13/07 21:45</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>60.00</t>
-        </is>
+      <c r="F2" t="n">
+        <v>60</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -521,7 +519,7 @@
         </is>
       </c>
       <c r="I2" s="2" t="n">
-        <v>45851.08645478688</v>
+        <v>45851.08645479166</v>
       </c>
     </row>
     <row r="3">
@@ -550,10 +548,8 @@
           <t>13/07 22:15</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>55.00</t>
-        </is>
+      <c r="F3" t="n">
+        <v>55</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -566,7 +562,7 @@
         </is>
       </c>
       <c r="I3" s="2" t="n">
-        <v>45851.08645478688</v>
+        <v>45851.08645479166</v>
       </c>
     </row>
     <row r="4">
@@ -595,10 +591,8 @@
           <t>18/07 23:00</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>50.00</t>
-        </is>
+      <c r="F4" t="n">
+        <v>50</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -611,7 +605,7 @@
         </is>
       </c>
       <c r="I4" s="2" t="n">
-        <v>45851.08645478688</v>
+        <v>45851.08645479166</v>
       </c>
     </row>
     <row r="5">
@@ -640,10 +634,8 @@
           <t>14/07 19:30</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>60.00</t>
-        </is>
+      <c r="F5" t="n">
+        <v>60</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -656,7 +648,7 @@
         </is>
       </c>
       <c r="I5" s="2" t="n">
-        <v>45851.08645478688</v>
+        <v>45851.08645479166</v>
       </c>
     </row>
     <row r="6">
@@ -685,10 +677,8 @@
           <t>13/07 17:15</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>55.00</t>
-        </is>
+      <c r="F6" t="n">
+        <v>55</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -701,7 +691,7 @@
         </is>
       </c>
       <c r="I6" s="2" t="n">
-        <v>45851.08645478688</v>
+        <v>45851.08645479166</v>
       </c>
     </row>
     <row r="7">
@@ -730,10 +720,8 @@
           <t>20/07 13:00</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>50.00</t>
-        </is>
+      <c r="F7" t="n">
+        <v>50</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -746,7 +734,7 @@
         </is>
       </c>
       <c r="I7" s="2" t="n">
-        <v>45851.08645478688</v>
+        <v>45851.08645479166</v>
       </c>
     </row>
     <row r="8">
@@ -775,10 +763,8 @@
           <t>13/07 14:30</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>55.00</t>
-        </is>
+      <c r="F8" t="n">
+        <v>55</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -791,7 +777,7 @@
         </is>
       </c>
       <c r="I8" s="2" t="n">
-        <v>45851.08645478688</v>
+        <v>45851.08645479166</v>
       </c>
     </row>
     <row r="9">
@@ -820,10 +806,8 @@
           <t>19/07 21:45</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>60.00</t>
-        </is>
+      <c r="F9" t="n">
+        <v>60</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -836,7 +820,7 @@
         </is>
       </c>
       <c r="I9" s="2" t="n">
-        <v>45851.08645478688</v>
+        <v>45851.08645479166</v>
       </c>
     </row>
     <row r="10">
@@ -865,10 +849,8 @@
           <t>20/07 00:00</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>50.00</t>
-        </is>
+      <c r="F10" t="n">
+        <v>50</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -881,7 +863,7 @@
         </is>
       </c>
       <c r="I10" s="2" t="n">
-        <v>45851.08645478688</v>
+        <v>45851.08645479166</v>
       </c>
     </row>
     <row r="11">
@@ -910,10 +892,8 @@
           <t>13/07 19:00</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>55.00</t>
-        </is>
+      <c r="F11" t="n">
+        <v>55</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -926,7 +906,7 @@
         </is>
       </c>
       <c r="I11" s="2" t="n">
-        <v>45851.08645478688</v>
+        <v>45851.08645479166</v>
       </c>
     </row>
     <row r="12">
@@ -955,10 +935,8 @@
           <t>16/07 00:30</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>45.00</t>
-        </is>
+      <c r="F12" t="n">
+        <v>45</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -971,7 +949,7 @@
         </is>
       </c>
       <c r="I12" s="2" t="n">
-        <v>45851.08645478688</v>
+        <v>45851.08645479166</v>
       </c>
     </row>
     <row r="13">
@@ -1000,10 +978,8 @@
           <t>16/07 00:30</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>45.00</t>
-        </is>
+      <c r="F13" t="n">
+        <v>45</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -1016,7 +992,7 @@
         </is>
       </c>
       <c r="I13" s="2" t="n">
-        <v>45851.08645478688</v>
+        <v>45851.08645479166</v>
       </c>
     </row>
     <row r="14">
@@ -1045,10 +1021,8 @@
           <t>16/07 22:00</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>50.00</t>
-        </is>
+      <c r="F14" t="n">
+        <v>50</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -1061,7 +1035,7 @@
         </is>
       </c>
       <c r="I14" s="2" t="n">
-        <v>45851.08645478688</v>
+        <v>45851.08645479166</v>
       </c>
     </row>
     <row r="15">
@@ -1090,10 +1064,8 @@
           <t>17/07 00:30</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>50.00</t>
-        </is>
+      <c r="F15" t="n">
+        <v>50</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -1106,7 +1078,7 @@
         </is>
       </c>
       <c r="I15" s="2" t="n">
-        <v>45851.08645478688</v>
+        <v>45851.08645479166</v>
       </c>
     </row>
     <row r="16">
@@ -1135,10 +1107,8 @@
           <t>17/07 01:00</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>45.00</t>
-        </is>
+      <c r="F16" t="n">
+        <v>45</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -1151,7 +1121,7 @@
         </is>
       </c>
       <c r="I16" s="2" t="n">
-        <v>45851.08645478688</v>
+        <v>45851.08645479166</v>
       </c>
     </row>
     <row r="17">
@@ -1180,10 +1150,8 @@
           <t>19/07 21:45</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>45.00</t>
-        </is>
+      <c r="F17" t="n">
+        <v>45</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -1196,7 +1164,7 @@
         </is>
       </c>
       <c r="I17" s="2" t="n">
-        <v>45851.08645478688</v>
+        <v>45851.08645479166</v>
       </c>
     </row>
     <row r="18">
@@ -1225,10 +1193,8 @@
           <t>20/07 13:00</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>40.00</t>
-        </is>
+      <c r="F18" t="n">
+        <v>40</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1241,7 +1207,7 @@
         </is>
       </c>
       <c r="I18" s="2" t="n">
-        <v>45851.08645478688</v>
+        <v>45851.08645479166</v>
       </c>
     </row>
     <row r="19">
@@ -1270,10 +1236,8 @@
           <t>22/07 00:15</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>40.00</t>
-        </is>
+      <c r="F19" t="n">
+        <v>40</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -1286,7 +1250,7 @@
         </is>
       </c>
       <c r="I19" s="2" t="n">
-        <v>45851.08645478688</v>
+        <v>45851.08645479166</v>
       </c>
     </row>
     <row r="20">
@@ -1315,10 +1279,8 @@
           <t>17/07 16:00</t>
         </is>
       </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>45.00</t>
-        </is>
+      <c r="F20" t="n">
+        <v>45</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -1331,7 +1293,7 @@
         </is>
       </c>
       <c r="I20" s="2" t="n">
-        <v>45851.08645478688</v>
+        <v>45851.08645479166</v>
       </c>
     </row>
     <row r="21">
@@ -1360,10 +1322,8 @@
           <t>22/07 17:00</t>
         </is>
       </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>50.00</t>
-        </is>
+      <c r="F21" t="n">
+        <v>50</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -1376,7 +1336,7 @@
         </is>
       </c>
       <c r="I21" s="2" t="n">
-        <v>45851.08645478688</v>
+        <v>45851.08645479166</v>
       </c>
     </row>
     <row r="22">
@@ -1405,10 +1365,8 @@
           <t>13/07 23:00</t>
         </is>
       </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>3.50</t>
-        </is>
+      <c r="F22" t="n">
+        <v>3.5</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -1421,7 +1379,142 @@
         </is>
       </c>
       <c r="I22" s="2" t="n">
-        <v>45851.08645478688</v>
+        <v>45851.08645479166</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 3.51re équipe | Fagiano Ok</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Fagiano Okayama – Vissel KobeJ-League</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Plus que 3.51re équipe</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>20/07 10:00</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>60.00</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>1,74%</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>+4,37%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="n">
+        <v>45851.16759559337</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 3.52e équipe | Corinthian</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Corinthians – Red Bull BragantinoSérie A</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Plus que 3.52e équipe</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>13/07 22:00</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>45.00</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>2,24%</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>+0,94%</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="n">
+        <v>45851.16759559337</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 5.5 | Velez Sars</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Velez Sarsfield – CA TigreLiga Profesional</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Plus que 5.5</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>15/07 00:15</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>50.00</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>2,01%</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>+0,33%</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="n">
+        <v>45851.16759559337</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-07-13.xlsx
+++ b/data/valuebets_database_2025-07-13.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I25"/>
+  <dimension ref="A1:I28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1408,10 +1408,8 @@
           <t>20/07 10:00</t>
         </is>
       </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>60.00</t>
-        </is>
+      <c r="F23" t="n">
+        <v>60</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
@@ -1424,7 +1422,7 @@
         </is>
       </c>
       <c r="I23" s="2" t="n">
-        <v>45851.16759559337</v>
+        <v>45851.16759559028</v>
       </c>
     </row>
     <row r="24">
@@ -1453,10 +1451,8 @@
           <t>13/07 22:00</t>
         </is>
       </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>45.00</t>
-        </is>
+      <c r="F24" t="n">
+        <v>45</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
@@ -1469,7 +1465,7 @@
         </is>
       </c>
       <c r="I24" s="2" t="n">
-        <v>45851.16759559337</v>
+        <v>45851.16759559028</v>
       </c>
     </row>
     <row r="25">
@@ -1498,10 +1494,8 @@
           <t>15/07 00:15</t>
         </is>
       </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>50.00</t>
-        </is>
+      <c r="F25" t="n">
+        <v>50</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
@@ -1514,7 +1508,142 @@
         </is>
       </c>
       <c r="I25" s="2" t="n">
-        <v>45851.16759559337</v>
+        <v>45851.16759559028</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unibet(FR)Tennis | H 1 (−1.5) | Rejchtman </t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Tennis</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Rejchtman Vinciguerra, William – Jesper De JongATP 250 Bastad</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>H 1 (−1.5)</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>14/07 08:30</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>65.00</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>2,02%</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>+31,1%</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="n">
+        <v>45851.22530880819</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 3.52e équipe | Estudiante</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Estudiantes de La Plata – CA HuracanLiga Profesional</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Plus que 3.52e équipe</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>21/07 22:00</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>45.00</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>2,29%</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>+2,93%</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="n">
+        <v>45851.22530880819</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 3.51re équipe | Tokyo Verd</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Tokyo Verdy – Machida ZelviaJ-League</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Plus que 3.51re équipe</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>20/07 09:00</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>55.00</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>1,84%</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>+1,38%</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="n">
+        <v>45851.22530880819</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-07-13.xlsx
+++ b/data/valuebets_database_2025-07-13.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I28"/>
+  <dimension ref="A1:I29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1537,10 +1537,8 @@
           <t>14/07 08:30</t>
         </is>
       </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>65.00</t>
-        </is>
+      <c r="F26" t="n">
+        <v>65</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
@@ -1553,7 +1551,7 @@
         </is>
       </c>
       <c r="I26" s="2" t="n">
-        <v>45851.22530880819</v>
+        <v>45851.22530880787</v>
       </c>
     </row>
     <row r="27">
@@ -1582,10 +1580,8 @@
           <t>21/07 22:00</t>
         </is>
       </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>45.00</t>
-        </is>
+      <c r="F27" t="n">
+        <v>45</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
@@ -1598,7 +1594,7 @@
         </is>
       </c>
       <c r="I27" s="2" t="n">
-        <v>45851.22530880819</v>
+        <v>45851.22530880787</v>
       </c>
     </row>
     <row r="28">
@@ -1627,10 +1623,8 @@
           <t>20/07 09:00</t>
         </is>
       </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>55.00</t>
-        </is>
+      <c r="F28" t="n">
+        <v>55</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
@@ -1643,7 +1637,52 @@
         </is>
       </c>
       <c r="I28" s="2" t="n">
-        <v>45851.22530880819</v>
+        <v>45851.22530880787</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football | Plus que 6.5 - tir cadré1re équipe | Corinthian</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Corinthians – BragantinoBrésil - Brésil Série A</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Plus que 6.5 - tir cadré1re équipe</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>13/07 22:00</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>4.75</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>25,2%</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>+19,5%</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="n">
+        <v>45851.27295309987</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-07-13.xlsx
+++ b/data/valuebets_database_2025-07-13.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I29"/>
+  <dimension ref="A1:I31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1666,10 +1666,8 @@
           <t>13/07 22:00</t>
         </is>
       </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>4.75</t>
-        </is>
+      <c r="F29" t="n">
+        <v>4.75</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
@@ -1682,7 +1680,97 @@
         </is>
       </c>
       <c r="I29" s="2" t="n">
-        <v>45851.27295309987</v>
+        <v>45851.27295310185</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football | Plus que 10.5 - tir cadré | Corinthian</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Corinthians – BragantinoBrésil - Brésil Série A</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Plus que 10.5 - tir cadré</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>13/07 22:00</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>3.90</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>26,6%</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>+3,71%</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="n">
+        <v>45851.30759115168</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Winamax(FR)Football | 1X | Viktoria P</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Winamax(FR)Football</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Viktoria Plzen – Servette FCEurope - Ligue des Champions</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>1X</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>22/07 17:00</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>1.20</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>83,8%</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>+0,52%</t>
+        </is>
+      </c>
+      <c r="I31" s="2" t="n">
+        <v>45851.30759115168</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-07-13.xlsx
+++ b/data/valuebets_database_2025-07-13.xlsx
@@ -1709,10 +1709,8 @@
           <t>13/07 22:00</t>
         </is>
       </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>3.90</t>
-        </is>
+      <c r="F30" t="n">
+        <v>3.9</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
@@ -1725,7 +1723,7 @@
         </is>
       </c>
       <c r="I30" s="2" t="n">
-        <v>45851.30759115168</v>
+        <v>45851.30759115741</v>
       </c>
     </row>
     <row r="31">
@@ -1754,10 +1752,8 @@
           <t>22/07 17:00</t>
         </is>
       </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>1.20</t>
-        </is>
+      <c r="F31" t="n">
+        <v>1.2</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
@@ -1770,7 +1766,7 @@
         </is>
       </c>
       <c r="I31" s="2" t="n">
-        <v>45851.30759115168</v>
+        <v>45851.30759115741</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-07-13.xlsx
+++ b/data/valuebets_database_2025-07-13.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I31"/>
+  <dimension ref="A1:I32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1769,6 +1769,51 @@
         <v>45851.30759115741</v>
       </c>
     </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BetClic(FR)Football | Moins que 8.5 - tir cadré | St. Louis </t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>St. Louis City SC – Portland TimbersÉtats-Unis - États-Unis MLS</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Moins que 8.5 - tir cadré</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>13/07 23:00</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>3.10</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>38,3%</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>+18,7%</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="n">
+        <v>45851.39225837647</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/valuebets_database_2025-07-13.xlsx
+++ b/data/valuebets_database_2025-07-13.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I32"/>
+  <dimension ref="A1:I35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1795,10 +1795,8 @@
           <t>13/07 23:00</t>
         </is>
       </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>3.10</t>
-        </is>
+      <c r="F32" t="n">
+        <v>3.1</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
@@ -1811,7 +1809,142 @@
         </is>
       </c>
       <c r="I32" s="2" t="n">
-        <v>45851.39225837647</v>
+        <v>45851.39225837963</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football | Moins que 19.5 - tirs1re équipe | Angleterre</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Angleterre F. – Pays de Galles F.Europe - Euro Féminin 2025</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Moins que 19.5 - tirs1re équipe</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>13/07 19:00</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>2.48</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>45,7%</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>+13,3%</t>
+        </is>
+      </c>
+      <c r="I33" s="2" t="n">
+        <v>45851.43410951005</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unibet(FR)Football | Plus que 3.51re équipe | Osters IF </t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Osters IF – Malmo FFAllsvenskan</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Plus que 3.51re équipe</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>19/07 13:00</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>50.00</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>2,26%</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>+12,8%</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="n">
+        <v>45851.43410951005</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football | Moins que 9.5 - tirs1re équipe | Pays-Bas F</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Pays-Bas F. – France F.Europe - Euro Féminin 2025</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Moins que 9.5 - tirs1re équipe</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>13/07 19:00</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>2.23</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>46,7%</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>+4,23%</t>
+        </is>
+      </c>
+      <c r="I35" s="2" t="n">
+        <v>45851.43410951005</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-07-13.xlsx
+++ b/data/valuebets_database_2025-07-13.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I35"/>
+  <dimension ref="A1:I36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1838,10 +1838,8 @@
           <t>13/07 19:00</t>
         </is>
       </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>2.48</t>
-        </is>
+      <c r="F33" t="n">
+        <v>2.48</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
@@ -1854,7 +1852,7 @@
         </is>
       </c>
       <c r="I33" s="2" t="n">
-        <v>45851.43410951005</v>
+        <v>45851.43410951389</v>
       </c>
     </row>
     <row r="34">
@@ -1883,10 +1881,8 @@
           <t>19/07 13:00</t>
         </is>
       </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>50.00</t>
-        </is>
+      <c r="F34" t="n">
+        <v>50</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
@@ -1899,7 +1895,7 @@
         </is>
       </c>
       <c r="I34" s="2" t="n">
-        <v>45851.43410951005</v>
+        <v>45851.43410951389</v>
       </c>
     </row>
     <row r="35">
@@ -1928,10 +1924,8 @@
           <t>13/07 19:00</t>
         </is>
       </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>2.23</t>
-        </is>
+      <c r="F35" t="n">
+        <v>2.23</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
@@ -1944,7 +1938,52 @@
         </is>
       </c>
       <c r="I35" s="2" t="n">
-        <v>45851.43410951005</v>
+        <v>45851.43410951389</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unibet(FR)Football | Plus que 3.52e équipe | San Diego </t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>San Diego FC – Toronto FCMLS</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Plus que 3.52e équipe</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>17/07 02:30</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>60.00</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>2,18%</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>+31,0%</t>
+        </is>
+      </c>
+      <c r="I36" s="2" t="n">
+        <v>45851.47137166825</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-07-13.xlsx
+++ b/data/valuebets_database_2025-07-13.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I36"/>
+  <dimension ref="A1:I38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1967,10 +1967,8 @@
           <t>17/07 02:30</t>
         </is>
       </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>60.00</t>
-        </is>
+      <c r="F36" t="n">
+        <v>60</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
@@ -1983,7 +1981,97 @@
         </is>
       </c>
       <c r="I36" s="2" t="n">
-        <v>45851.47137166825</v>
+        <v>45851.47137166667</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BetClic(FR)Football | Plus que 11.5 - tir cadré | St. Louis </t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>St. Louis City SC – Portland TimbersÉtats-Unis - États-Unis MLS</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Plus que 11.5 - tir cadré</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>13/07 23:00</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>29,8%</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>+4,18%</t>
+        </is>
+      </c>
+      <c r="I37" s="2" t="n">
+        <v>45851.52962035806</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Winamax(FR)Tennis | 21-2 | Elias Ymer</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Winamax(FR)Tennis</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Elias Ymer – Tristan BoyerATP - Bastad</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>21-2</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>14/07 08:30</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>2.10</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>48,8%</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>+2,43%</t>
+        </is>
+      </c>
+      <c r="I38" s="2" t="n">
+        <v>45851.52962035806</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-07-13.xlsx
+++ b/data/valuebets_database_2025-07-13.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I38"/>
+  <dimension ref="A1:I39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2010,10 +2010,8 @@
           <t>13/07 23:00</t>
         </is>
       </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>3.50</t>
-        </is>
+      <c r="F37" t="n">
+        <v>3.5</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
@@ -2026,7 +2024,7 @@
         </is>
       </c>
       <c r="I37" s="2" t="n">
-        <v>45851.52962035806</v>
+        <v>45851.52962035879</v>
       </c>
     </row>
     <row r="38">
@@ -2055,10 +2053,8 @@
           <t>14/07 08:30</t>
         </is>
       </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>2.10</t>
-        </is>
+      <c r="F38" t="n">
+        <v>2.1</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
@@ -2071,7 +2067,52 @@
         </is>
       </c>
       <c r="I38" s="2" t="n">
-        <v>45851.52962035806</v>
+        <v>45851.52962035879</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>PokerStars(FR)Basketball | X2e période[race to 15 regular time] | Washington</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>PokerStars(FR)Basketball</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Washington Mystics – Seattle StormUSA - WNBA</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>X2e période[race to 15 regular time]</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>13/07 22:00</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>25.00</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>4,04%</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>+1,05%</t>
+        </is>
+      </c>
+      <c r="I39" s="2" t="n">
+        <v>45851.56356986579</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-07-13.xlsx
+++ b/data/valuebets_database_2025-07-13.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I39"/>
+  <dimension ref="A1:I40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2096,10 +2096,8 @@
           <t>13/07 22:00</t>
         </is>
       </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>25.00</t>
-        </is>
+      <c r="F39" t="n">
+        <v>25</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
@@ -2112,7 +2110,52 @@
         </is>
       </c>
       <c r="I39" s="2" t="n">
-        <v>45851.56356986579</v>
+        <v>45851.56356986111</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Winamax(FR)Football | Moins que 19.5 - tirs1re équipe | Angleterre</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Winamax(FR)Football</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Angleterre (F) – Pays de Galles (F)Europe - Euro (F)</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Moins que 19.5 - tirs1re équipe</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>13/07 19:00</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>2.35</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>44,2%</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>+3,78%</t>
+        </is>
+      </c>
+      <c r="I40" s="2" t="n">
+        <v>45851.59711086911</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-07-13.xlsx
+++ b/data/valuebets_database_2025-07-13.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I40"/>
+  <dimension ref="A1:I44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2139,10 +2139,8 @@
           <t>13/07 19:00</t>
         </is>
       </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>2.35</t>
-        </is>
+      <c r="F40" t="n">
+        <v>2.35</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
@@ -2155,7 +2153,187 @@
         </is>
       </c>
       <c r="I40" s="2" t="n">
-        <v>45851.59711086911</v>
+        <v>45851.59711086805</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football | Plus que 28.5 - tirs | Corinthian</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Corinthians – BragantinoBrésil - Brésil Série A</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Plus que 28.5 - tirs</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>13/07 22:00</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>2.80</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>38,8%</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>+8,74%</t>
+        </is>
+      </c>
+      <c r="I41" s="2" t="n">
+        <v>45851.64005634302</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BetClic(FR)Football | Plus que 5.5 - tir cadré1re équipe | St. Louis </t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>St. Louis City SC – Portland TimbersÉtats-Unis - États-Unis MLS</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Plus que 5.5 - tir cadré1re équipe</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>13/07 23:00</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>2.25</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>45,9%</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>+3,27%</t>
+        </is>
+      </c>
+      <c r="I42" s="2" t="n">
+        <v>45851.64005634302</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Betsson(FR)Football | Pas de buts | Pays-Bas –</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Betsson(FR)Football</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Pays-Bas – FranceInternational - Euro 2025 (F)</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>13/07 19:00</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>17.50</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>5,81%</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>+1,66%</t>
+        </is>
+      </c>
+      <c r="I43" s="2" t="n">
+        <v>45851.64005634302</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Winamax(FR)Football | Moins que 5 | Viktoria P</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Winamax(FR)Football</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Viktoria Plzen – Servette FCEurope - Ligue des Champions</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>Moins que 5</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>22/07 17:00</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>1.07</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>94,4%</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>+1,02%</t>
+        </is>
+      </c>
+      <c r="I44" s="2" t="n">
+        <v>45851.64005634302</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-07-13.xlsx
+++ b/data/valuebets_database_2025-07-13.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I44"/>
+  <dimension ref="A1:I46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2182,10 +2182,8 @@
           <t>13/07 22:00</t>
         </is>
       </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>2.80</t>
-        </is>
+      <c r="F41" t="n">
+        <v>2.8</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
@@ -2198,7 +2196,7 @@
         </is>
       </c>
       <c r="I41" s="2" t="n">
-        <v>45851.64005634302</v>
+        <v>45851.64005634259</v>
       </c>
     </row>
     <row r="42">
@@ -2227,10 +2225,8 @@
           <t>13/07 23:00</t>
         </is>
       </c>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t>2.25</t>
-        </is>
+      <c r="F42" t="n">
+        <v>2.25</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
@@ -2243,7 +2239,7 @@
         </is>
       </c>
       <c r="I42" s="2" t="n">
-        <v>45851.64005634302</v>
+        <v>45851.64005634259</v>
       </c>
     </row>
     <row r="43">
@@ -2272,10 +2268,8 @@
           <t>13/07 19:00</t>
         </is>
       </c>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t>17.50</t>
-        </is>
+      <c r="F43" t="n">
+        <v>17.5</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
@@ -2288,7 +2282,7 @@
         </is>
       </c>
       <c r="I43" s="2" t="n">
-        <v>45851.64005634302</v>
+        <v>45851.64005634259</v>
       </c>
     </row>
     <row r="44">
@@ -2317,10 +2311,8 @@
           <t>22/07 17:00</t>
         </is>
       </c>
-      <c r="F44" t="inlineStr">
-        <is>
-          <t>1.07</t>
-        </is>
+      <c r="F44" t="n">
+        <v>1.07</v>
       </c>
       <c r="G44" t="inlineStr">
         <is>
@@ -2333,7 +2325,97 @@
         </is>
       </c>
       <c r="I44" s="2" t="n">
-        <v>45851.64005634302</v>
+        <v>45851.64005634259</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 3.52e équipe | Atletico T</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Atletico Tucuman – Central CordobaLiga Profesional</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>Plus que 3.52e équipe</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>19/07 00:30</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>40.00</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>2,67%</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>+6,94%</t>
+        </is>
+      </c>
+      <c r="I45" s="2" t="n">
+        <v>45851.68521467005</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BetClic(FR)Football | Plus que 6.5 - tir cadré1re équipe | St. Louis </t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>St. Louis City SC – Portland TimbersÉtats-Unis - États-Unis MLS</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>Plus que 6.5 - tir cadré1re équipe</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>13/07 23:00</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>30,7%</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>+4,22%</t>
+        </is>
+      </c>
+      <c r="I46" s="2" t="n">
+        <v>45851.68521467005</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-07-13.xlsx
+++ b/data/valuebets_database_2025-07-13.xlsx
@@ -2354,10 +2354,8 @@
           <t>19/07 00:30</t>
         </is>
       </c>
-      <c r="F45" t="inlineStr">
-        <is>
-          <t>40.00</t>
-        </is>
+      <c r="F45" t="n">
+        <v>40</v>
       </c>
       <c r="G45" t="inlineStr">
         <is>
@@ -2370,7 +2368,7 @@
         </is>
       </c>
       <c r="I45" s="2" t="n">
-        <v>45851.68521467005</v>
+        <v>45851.68521466435</v>
       </c>
     </row>
     <row r="46">
@@ -2399,10 +2397,8 @@
           <t>13/07 23:00</t>
         </is>
       </c>
-      <c r="F46" t="inlineStr">
-        <is>
-          <t>3.40</t>
-        </is>
+      <c r="F46" t="n">
+        <v>3.4</v>
       </c>
       <c r="G46" t="inlineStr">
         <is>
@@ -2415,7 +2411,7 @@
         </is>
       </c>
       <c r="I46" s="2" t="n">
-        <v>45851.68521467005</v>
+        <v>45851.68521466435</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-07-13.xlsx
+++ b/data/valuebets_database_2025-07-13.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I46"/>
+  <dimension ref="A1:I47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2414,6 +2414,51 @@
         <v>45851.68521466435</v>
       </c>
     </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 3.52e équipe | CA Indepen</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>CA Independiente – Talleres de CordobaLiga Profesional</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>Plus que 3.52e équipe</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>21/07 00:00</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>55.00</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>2,34%</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>+28,5%</t>
+        </is>
+      </c>
+      <c r="I47" s="2" t="n">
+        <v>45851.77079391267</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/valuebets_database_2025-07-13.xlsx
+++ b/data/valuebets_database_2025-07-13.xlsx
@@ -2440,10 +2440,8 @@
           <t>21/07 00:00</t>
         </is>
       </c>
-      <c r="F47" t="inlineStr">
-        <is>
-          <t>55.00</t>
-        </is>
+      <c r="F47" t="n">
+        <v>55</v>
       </c>
       <c r="G47" t="inlineStr">
         <is>
@@ -2456,7 +2454,7 @@
         </is>
       </c>
       <c r="I47" s="2" t="n">
-        <v>45851.77079391267</v>
+        <v>45851.77079391204</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-07-13.xlsx
+++ b/data/valuebets_database_2025-07-13.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I47"/>
+  <dimension ref="A1:I49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2457,6 +2457,96 @@
         <v>45851.77079391204</v>
       </c>
     </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 5.5 | Argentinos</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Argentinos Juniors – Boca JuniorsLiga Profesional</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>Plus que 5.5</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>13/07 21:45</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>50.00</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>2,04%</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>+1,78%</t>
+        </is>
+      </c>
+      <c r="I48" s="2" t="n">
+        <v>45851.84966238439</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 3.51re équipe | Santos – F</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Santos – FlamengoSérie A</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>Plus que 3.51re équipe</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>16/07 23:00</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>45.00</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>2,25%</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>+1,08%</t>
+        </is>
+      </c>
+      <c r="I49" s="2" t="n">
+        <v>45851.84966238439</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/valuebets_database_2025-07-13.xlsx
+++ b/data/valuebets_database_2025-07-13.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I49"/>
+  <dimension ref="A1:I50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2483,10 +2483,8 @@
           <t>13/07 21:45</t>
         </is>
       </c>
-      <c r="F48" t="inlineStr">
-        <is>
-          <t>50.00</t>
-        </is>
+      <c r="F48" t="n">
+        <v>50</v>
       </c>
       <c r="G48" t="inlineStr">
         <is>
@@ -2499,7 +2497,7 @@
         </is>
       </c>
       <c r="I48" s="2" t="n">
-        <v>45851.84966238439</v>
+        <v>45851.84966238426</v>
       </c>
     </row>
     <row r="49">
@@ -2528,10 +2526,8 @@
           <t>16/07 23:00</t>
         </is>
       </c>
-      <c r="F49" t="inlineStr">
-        <is>
-          <t>45.00</t>
-        </is>
+      <c r="F49" t="n">
+        <v>45</v>
       </c>
       <c r="G49" t="inlineStr">
         <is>
@@ -2544,7 +2540,52 @@
         </is>
       </c>
       <c r="I49" s="2" t="n">
-        <v>45851.84966238439</v>
+        <v>45851.84966238426</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 3.51re équipe | FK Pardubi</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>FK Pardubice – FC Viktoria PlzenSynot League</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>Plus que 3.51re équipe</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>18/07 17:00</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>60.00</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>2,42%</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>+45,3%</t>
+        </is>
+      </c>
+      <c r="I50" s="2" t="n">
+        <v>45851.88923555634</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-07-13.xlsx
+++ b/data/valuebets_database_2025-07-13.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I50"/>
+  <dimension ref="A1:I52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2569,10 +2569,8 @@
           <t>18/07 17:00</t>
         </is>
       </c>
-      <c r="F50" t="inlineStr">
-        <is>
-          <t>60.00</t>
-        </is>
+      <c r="F50" t="n">
+        <v>60</v>
       </c>
       <c r="G50" t="inlineStr">
         <is>
@@ -2585,7 +2583,97 @@
         </is>
       </c>
       <c r="I50" s="2" t="n">
-        <v>45851.88923555634</v>
+        <v>45851.88923555556</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 3.52e équipe | FC Univers</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>FC Universitatea Cluj – UTA AradLiga 1</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>Plus que 3.52e équipe</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>19/07 15:30</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>45.00</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>2,51%</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>+12,7%</t>
+        </is>
+      </c>
+      <c r="I51" s="2" t="n">
+        <v>45851.93166065486</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 3.52e équipe | Central Co</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Central Cordoba – Cerro Largo FCCopa Sudamericana</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>Plus que 3.52e équipe</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>15/07 22:00</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>40.00</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>2,56%</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>+2,24%</t>
+        </is>
+      </c>
+      <c r="I52" s="2" t="n">
+        <v>45851.93166065486</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-07-13.xlsx
+++ b/data/valuebets_database_2025-07-13.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I52"/>
+  <dimension ref="A1:I55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2612,10 +2612,8 @@
           <t>19/07 15:30</t>
         </is>
       </c>
-      <c r="F51" t="inlineStr">
-        <is>
-          <t>45.00</t>
-        </is>
+      <c r="F51" t="n">
+        <v>45</v>
       </c>
       <c r="G51" t="inlineStr">
         <is>
@@ -2628,7 +2626,7 @@
         </is>
       </c>
       <c r="I51" s="2" t="n">
-        <v>45851.93166065486</v>
+        <v>45851.93166065972</v>
       </c>
     </row>
     <row r="52">
@@ -2657,23 +2655,156 @@
           <t>15/07 22:00</t>
         </is>
       </c>
-      <c r="F52" t="inlineStr">
+      <c r="F52" t="n">
+        <v>40</v>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>2,56%</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>+2,24%</t>
+        </is>
+      </c>
+      <c r="I52" s="2" t="n">
+        <v>45851.93166065972</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 3.52e équipe | Deportes T</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Deportes Tolima – Santa FePrimera A</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>Plus que 3.52e équipe</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>19/07 01:10</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
         <is>
           <t>40.00</t>
         </is>
       </c>
-      <c r="G52" t="inlineStr">
-        <is>
-          <t>2,56%</t>
-        </is>
-      </c>
-      <c r="H52" t="inlineStr">
-        <is>
-          <t>+2,24%</t>
-        </is>
-      </c>
-      <c r="I52" s="2" t="n">
-        <v>45851.93166065486</v>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>2,80%</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>+11,8%</t>
+        </is>
+      </c>
+      <c r="I53" s="2" t="n">
+        <v>45851.97426399674</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unibet(FR)Football | Plus que 3.52e équipe | BK Hacken </t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>BK Hacken – Spartak TrnavaLigue Europa</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>Plus que 3.52e équipe</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>17/07 17:00</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>40.00</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>2,61%</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>+4,43%</t>
+        </is>
+      </c>
+      <c r="I54" s="2" t="n">
+        <v>45851.97426399674</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unibet(FR)Football | Plus que 3.52e équipe | Fortaleza </t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Fortaleza – Ceara SCSérie A</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>Plus que 3.52e équipe</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>13/07 23:30</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>45.00</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>2,26%</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>+1,69%</t>
+        </is>
+      </c>
+      <c r="I55" s="2" t="n">
+        <v>45851.97426399674</v>
       </c>
     </row>
   </sheetData>
